--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484663_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484663_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9952</v>
+        <v>3.4322</v>
       </c>
       <c r="E2" t="n">
-        <v>2.726</v>
+        <v>2.1631</v>
       </c>
       <c r="F2" t="n">
         <v>1.2691</v>
@@ -610,10 +610,10 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4201</v>
+        <v>-0.1429</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1991</v>
+        <v>-0.3639</v>
       </c>
       <c r="U2" t="n">
         <v>0.221</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.085</v>
+        <v>2.7204</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8989</v>
+        <v>3.3115</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.591</v>
       </c>
       <c r="G3" t="n">
         <v>0.4877</v>
@@ -688,13 +688,13 @@
         <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8792</v>
+        <v>-0.2438</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.5799</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1132</v>
+        <v>0.3361</v>
       </c>
       <c r="V3" t="n">
         <v>0.6439</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6022</v>
+        <v>0.3251</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2391</v>
+        <v>0.3251</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6368</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4078</v>
+        <v>0.3251</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1499</v>
+        <v>0.3251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5577</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1251</v>
+        <v>0.3251</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4644</v>
+        <v>0.3251</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2827</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3145</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0318</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3607</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3185</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>J. ROMERA GALINDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3251</v>
+        <v>0.0803</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3251</v>
+        <v>0.1472</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.067</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3251</v>
+        <v>-0.2403</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3251</v>
+        <v>-0.2403</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3251</v>
+        <v>0.065</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3251</v>
+        <v>0.065</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.3053</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3053</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0822</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.1282</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROMERA GALINDO</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1121</v>
+        <v>-0.2685</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0451</v>
+        <v>0.4427</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.067</v>
+        <v>-0.7111</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2403</v>
+        <v>-0.4078</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2403</v>
+        <v>0.1499</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.5577</v>
       </c>
       <c r="J6" t="n">
-        <v>0.065</v>
+        <v>-0.1251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.065</v>
+        <v>0.4644</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.5895</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3053</v>
+        <v>-0.2827</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3053</v>
+        <v>-0.3145</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2383</v>
+        <v>0.49</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1101</v>
+        <v>0.2459</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1282</v>
+        <v>0.2441</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1545</v>
+        <v>-0.9896</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8288</v>
+        <v>-2.4071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6743</v>
+        <v>1.4175</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.5489</v>
+        <v>-0.4557</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.5457</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0032</v>
+        <v>-0.5354</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2985</v>
+        <v>-0.7668</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.0009</v>
+        <v>-0.1675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7024</v>
+        <v>-0.5994</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2504</v>
+        <v>0.3112</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5448</v>
+        <v>0.2472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7056</v>
+        <v>0.064</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1154</v>
+        <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5514</v>
+        <v>-0.3665</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8469</v>
+        <v>-1.046</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3982</v>
+        <v>0.6795</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6439</v>
+        <v>-1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2328</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
         <v>-1.5889</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>E. CAMPOS MONTEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2098</v>
+        <v>-1.2156</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6273</v>
+        <v>-1.1899</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4175</v>
+        <v>-0.0257</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4557</v>
+        <v>-1.5223</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.2403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5354</v>
+        <v>-1.2821</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7668</v>
+        <v>-1.217</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1675</v>
+        <v>0.065</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5994</v>
+        <v>-1.2821</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3112</v>
+        <v>-0.3053</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2472</v>
+        <v>-0.3053</v>
       </c>
       <c r="O8" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5867</v>
+        <v>-0.0598</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2662</v>
+        <v>0.0272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6795</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. CAMPOS MONTEIRO</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4326</v>
+        <v>-1.6469</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3822</v>
+        <v>-1.8009</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0505</v>
+        <v>0.1541</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5223</v>
+        <v>-4.5489</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2403</v>
+        <v>-4.5457</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2821</v>
+        <v>-0.0032</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.217</v>
+        <v>-2.2985</v>
       </c>
       <c r="K9" t="n">
-        <v>0.065</v>
+        <v>-3.0009</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2821</v>
+        <v>0.7024</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3053</v>
+        <v>-2.2504</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3053</v>
+        <v>-1.5448</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.7056</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>2.1991</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>3.1154</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2768</v>
+        <v>0.059</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.819</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1117</v>
+        <v>0.878</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2328</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9979</v>
+        <v>-1.7058</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3821</v>
+        <v>-1.7185</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6158</v>
+        <v>0.0126</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9497</v>
+        <v>-4.8746</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6869</v>
+        <v>-3.7077</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2628</v>
+        <v>-1.1669</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1604</v>
+        <v>-3.6761</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5451</v>
+        <v>-2.4774</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6153</v>
+        <v>-1.1987</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7893</v>
+        <v>-1.1985</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1418</v>
+        <v>-1.2303</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3525</v>
+        <v>0.0318</v>
       </c>
       <c r="P10" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4593</v>
+        <v>-0.1923</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2217</v>
+        <v>-0.3039</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2376</v>
+        <v>0.1116</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>3.1778</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.1778</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1947</v>
+        <v>-1.7362</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4055</v>
+        <v>-1.3681</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2108</v>
+        <v>-0.368</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8746</v>
+        <v>-1.9497</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7077</v>
+        <v>-1.6869</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1669</v>
+        <v>-0.2628</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.6761</v>
+        <v>-1.1604</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4774</v>
+        <v>-0.5451</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1987</v>
+        <v>-0.6153</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1985</v>
+        <v>-0.7893</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2303</v>
+        <v>-1.1418</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0318</v>
+        <v>0.3525</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6812</v>
+        <v>-0.1976</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9909</v>
+        <v>-0.2077</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3098</v>
+        <v>0.0102</v>
       </c>
       <c r="V11" t="n">
-        <v>3.1778</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1778</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8071</v>
+        <v>-4.2405</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9255</v>
+        <v>-5.5798</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1184</v>
+        <v>1.3393</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6737</v>
+        <v>-4.1057</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6542</v>
+        <v>-1.0062</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0195</v>
+        <v>-3.0995</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5424</v>
+        <v>-3.7178</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2604</v>
+        <v>-0.5543</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2821</v>
+        <v>-3.1635</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1312</v>
+        <v>-0.3879</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3938</v>
+        <v>-0.4519</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0314</v>
+        <v>-0.7291</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5505</v>
+        <v>-0.9457</v>
       </c>
       <c r="U12" t="n">
-        <v>0.582</v>
+        <v>0.2166</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3011</v>
+        <v>-0.3219</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3011</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9695</v>
+        <v>-4.7193</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9372</v>
+        <v>-4.6642</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9677</v>
+        <v>-0.055</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1057</v>
+        <v>-3.6737</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0062</v>
+        <v>-1.6542</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0995</v>
+        <v>-2.0195</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7178</v>
+        <v>-2.5424</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5543</v>
+        <v>-1.2604</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.1635</v>
+        <v>-1.2821</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3879</v>
+        <v>-1.1312</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4519</v>
+        <v>-0.3938</v>
       </c>
       <c r="O13" t="n">
-        <v>0.064</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4581</v>
+        <v>0.1193</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3031</v>
+        <v>-0.2892</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.155</v>
+        <v>0.4085</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.8544</v>
+        <v>-5.1094</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.5574</v>
+        <v>-3.9114</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.297</v>
+        <v>-1.1979</v>
       </c>
       <c r="G14" t="n">
         <v>-5.4981</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.906</v>
+        <v>-0.161</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6802</v>
+        <v>-0.0343</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2258</v>
+        <v>-0.1267</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.7251</v>
+        <v>-15.0738</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.902</v>
+        <v>-16.2503</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1767</v>
+        <v>1.1769</v>
       </c>
       <c r="G15" t="n">
         <v>-25.2921</v>
@@ -1600,7 +1600,7 @@
         <v>-12.9939</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9375</v>
+        <v>-1.937499999999999</v>
       </c>
       <c r="L15" t="n">
         <v>-11.0569</v>
@@ -1618,19 +1618,19 @@
         <v>10.0791</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.330399999999999</v>
+        <v>-7.3304</v>
       </c>
       <c r="R15" t="n">
         <v>17.4094</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.122</v>
+        <v>-1.4707</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.8858</v>
+        <v>-4.2343</v>
       </c>
       <c r="U15" t="n">
-        <v>2.7639</v>
+        <v>2.763800000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.6097</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.0944</v>
+        <v>9.192</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1909</v>
+        <v>5.3832</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9036</v>
+        <v>3.8088</v>
       </c>
       <c r="G16" t="n">
         <v>8.128500000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.7573</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6244</v>
+        <v>-0.4321</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2842</v>
+        <v>1.1894</v>
       </c>
       <c r="V16" t="n">
         <v>1.5889</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4343</v>
+        <v>2.6266</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7563</v>
+        <v>0.9486</v>
       </c>
       <c r="F17" t="n">
         <v>1.678</v>
@@ -1780,10 +1780,10 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0905</v>
+        <v>0.1018</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5332</v>
+        <v>-0.3409</v>
       </c>
       <c r="U17" t="n">
         <v>0.4427</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3926</v>
+        <v>2.2315</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4631</v>
+        <v>2.7937</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9295</v>
+        <v>-0.5622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5306</v>
+        <v>4.0449</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2131</v>
+        <v>-0.9717</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3175</v>
+        <v>5.0165</v>
       </c>
       <c r="J18" t="n">
-        <v>1.041</v>
+        <v>3.2714</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2509</v>
+        <v>-0.6876</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2919</v>
+        <v>3.9591</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4896</v>
+        <v>0.7735</v>
       </c>
       <c r="N18" t="n">
-        <v>0.464</v>
+        <v>-0.284</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0256</v>
+        <v>1.0575</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9163</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0995</v>
+        <v>-2.9321</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7233</v>
+        <v>-0.0541</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5008</v>
+        <v>-0.0795</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2225</v>
+        <v>0.0254</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.945</v>
+        <v>0.6231</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0208</v>
+        <v>2.5339</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9658</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7464</v>
+        <v>2.2241</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2103</v>
+        <v>-0.061</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9567</v>
+        <v>2.2851</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5739</v>
+        <v>-0.2579</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4808</v>
+        <v>0.5018</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0931</v>
+        <v>-0.7597</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1728</v>
+        <v>-1.1537</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1054</v>
+        <v>0.0867</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0674</v>
+        <v>-1.2404</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4011</v>
+        <v>0.8958</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3754</v>
+        <v>0.4151</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0256</v>
+        <v>0.4807</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4553</v>
+        <v>0.3433</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5505</v>
+        <v>-0.4962</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0059</v>
+        <v>0.8395</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7201</v>
+        <v>1.6764</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5052</v>
+        <v>-1.2103</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7852</v>
+        <v>2.8867</v>
       </c>
       <c r="G20" t="n">
-        <v>4.0449</v>
+        <v>2.5739</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9717</v>
+        <v>1.4808</v>
       </c>
       <c r="I20" t="n">
-        <v>5.0165</v>
+        <v>1.0931</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2714</v>
+        <v>1.1728</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6876</v>
+        <v>1.1054</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9591</v>
+        <v>0.0674</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7735</v>
+        <v>1.4011</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.284</v>
+        <v>0.3754</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0575</v>
+        <v>1.0256</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3823</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9321</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5655</v>
+        <v>0.3854</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.368</v>
+        <v>-0.5505</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1975</v>
+        <v>0.9359</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.567</v>
+        <v>1.4617</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4456</v>
+        <v>0.3092</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0126</v>
+        <v>1.1525</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2579</v>
+        <v>2.5306</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5018</v>
+        <v>0.2131</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7597</v>
+        <v>2.3175</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1537</v>
+        <v>1.041</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0867</v>
+        <v>-0.2509</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2404</v>
+        <v>1.2919</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8958</v>
+        <v>1.4896</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4151</v>
+        <v>0.464</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4807</v>
+        <v>1.0256</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3138</v>
+        <v>0.7924</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8808</v>
+        <v>0.3469</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4455</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5889</v>
+        <v>-0.945</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5889</v>
+        <v>0.0208</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.317</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6814</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3644</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3452</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6851</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6601</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9687</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8854</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3765</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5768</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9768</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7127</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2642</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.5548</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.5548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.6017</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9122</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0.3105</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9752999999999999</v>
+        <v>2.3452</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.6851</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.6601</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9687</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.8854</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.3765</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.5768</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.2615</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.0565</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.5548</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.5548</v>
       </c>
     </row>
     <row r="24">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2213</v>
+        <v>-0.13</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2775</v>
+        <v>-1.989</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4988</v>
+        <v>1.859</v>
       </c>
       <c r="G25" t="n">
         <v>2.2635</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1411</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7715</v>
+        <v>-0.483</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9125</v>
+        <v>1.2728</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9005</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2922</v>
+        <v>-0.5782</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.8032</v>
+        <v>-5.5147</v>
       </c>
       <c r="F26" t="n">
-        <v>4.511</v>
+        <v>4.9365</v>
       </c>
       <c r="G26" t="n">
         <v>1.2111</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2596</v>
+        <v>0.4544</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.6293</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6582</v>
+        <v>1.0837</v>
       </c>
       <c r="V26" t="n">
         <v>0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.7763</v>
+        <v>-3.2401</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.3376</v>
+        <v>-4.0492</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5613</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-0.7892</v>
@@ -2560,13 +2560,13 @@
         <v>0.5498</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6048</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3311</v>
+        <v>-0.0426</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2738</v>
+        <v>-0.026</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>16.725</v>
+        <v>17.3661</v>
       </c>
       <c r="E28" t="n">
         <v>-1.1769</v>
       </c>
       <c r="F28" t="n">
-        <v>17.9019</v>
+        <v>18.5429</v>
       </c>
       <c r="G28" t="n">
         <v>25.2919</v>
@@ -2617,7 +2617,7 @@
         <v>8.609399999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>3.688400000000001</v>
+        <v>3.6884</v>
       </c>
       <c r="M28" t="n">
         <v>12.9942</v>
@@ -2638,13 +2638,13 @@
         <v>7.3304</v>
       </c>
       <c r="S28" t="n">
-        <v>3.122100000000001</v>
+        <v>3.7632</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.7638</v>
+        <v>-2.7637</v>
       </c>
       <c r="U28" t="n">
-        <v>5.8859</v>
+        <v>6.5269</v>
       </c>
       <c r="V28" t="n">
         <v>-1.6099</v>
